--- a/Payroll_Module_Status.xlsx
+++ b/Payroll_Module_Status.xlsx
@@ -831,9 +831,9 @@
           <t>Employees Attrition Rate</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — Joined/Left data hai; attrition % card pending</t>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — HR Analytics — Attrition % KPI (Iter 747)</t>
         </is>
       </c>
     </row>
@@ -855,9 +855,9 @@
           <t>Salary Virance from previous month</t>
         </is>
       </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — run compare hai; variance report pending</t>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — HR Analytics — Salary Variance KPI (prev vs current)</t>
         </is>
       </c>
     </row>
@@ -1344,9 +1344,9 @@
           <t>Reporting Manager &amp; Working Flow process</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — RM field + Approval Inbox hai; manager-chain pending</t>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — Org Hierarchy — Reporting Structure + chain-based approvals</t>
         </is>
       </c>
     </row>
@@ -1360,9 +1360,9 @@
           <t>Deptt Hierarchy process &amp; approval</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — Dept master + approvals hai; hierarchy chart pending</t>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — Org Hierarchy — Department hierarchy + workflow approvals</t>
         </is>
       </c>
     </row>
@@ -1392,9 +1392,9 @@
           <t>Org. Structure</t>
         </is>
       </c>
-      <c r="D74" s="9" t="inlineStr">
-        <is>
-          <t>❌ Not available — org chart abhi nahi</t>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — Org Structure module (departments + reporting chain)</t>
         </is>
       </c>
     </row>
@@ -1646,9 +1646,9 @@
           <t>Over Time Policy (Upto 48 Hrs restrict and calucate on over time rest hours will be transfer to other eraning)</t>
         </is>
       </c>
-      <c r="D91" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — OT calc full hai; 48-hr weekly cap rule pending</t>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — OT Policy — 48-hr cap + overflow rule</t>
         </is>
       </c>
     </row>
@@ -1678,9 +1678,9 @@
           <t>Minimum OT count 00:30 Minutes</t>
         </is>
       </c>
-      <c r="D93" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — OT rounding policy hai; 30-min minimum rule confirm/add</t>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — OT Policy — 30-min minimum rule</t>
         </is>
       </c>
     </row>
@@ -1726,9 +1726,9 @@
           <t>Overtime approval process</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — punch approvals hai; dedicated OT-hrs approval pending</t>
+      <c r="D96" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — OT approval workflow (Approval Inbox)</t>
         </is>
       </c>
     </row>
@@ -2252,9 +2252,9 @@
           <t>Reporting Manager &amp; Working Flow process</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — RM field + Approval Inbox hai; manager-chain pending</t>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — Org Hierarchy — Reporting Structure + chain-based approvals</t>
         </is>
       </c>
     </row>
@@ -2268,9 +2268,9 @@
           <t>Deptt Hierarchy process &amp; approval</t>
         </is>
       </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — Dept master + approvals hai; hierarchy chart pending</t>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — Org Hierarchy — Department hierarchy + workflow approvals</t>
         </is>
       </c>
     </row>
@@ -2300,9 +2300,9 @@
           <t>Org. Structure</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>❌ Not available — org chart abhi nahi</t>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — Org Structure module (departments + reporting chain)</t>
         </is>
       </c>
     </row>
@@ -2554,9 +2554,9 @@
           <t>Over Time Policy (Upto 48 Hrs restrict and calucate on over time rest hours will be transfer to other eraning)</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — OT calc full hai; 48-hr weekly cap rule pending</t>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — OT Policy — 48-hr cap + overflow rule</t>
         </is>
       </c>
     </row>
@@ -2586,9 +2586,9 @@
           <t>Minimum OT count 00:30 Minutes</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — OT rounding policy hai; 30-min minimum rule confirm/add</t>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — OT Policy — 30-min minimum rule</t>
         </is>
       </c>
     </row>
@@ -2634,9 +2634,9 @@
           <t>Overtime approval process</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
-        <is>
-          <t>🟡 Partial — punch approvals hai; dedicated OT-hrs approval pending</t>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>✅ Available — OT approval workflow (Approval Inbox)</t>
         </is>
       </c>
     </row>
